--- a/data/trans_dic/IP12B$abdomen-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$abdomen-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor abdominal</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor abdominal (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,09</t>
+          <t>0,0; 24,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,18</t>
+          <t>0,0; 46,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,07</t>
+          <t>0,0; 23,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,98</t>
+          <t>0,0; 34,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,04</t>
+          <t>0,0; 17,28</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,53</t>
+          <t>0,0; 34,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,87</t>
+          <t>0,0; 22,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,33</t>
+          <t>0,0; 57,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,96</t>
+          <t>0,0; 36,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,89</t>
+          <t>0,0; 39,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,25</t>
+          <t>0,0; 45,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,77</t>
+          <t>0,0; 55,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,34</t>
+          <t>0,0; 28,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,11</t>
+          <t>0,0; 31,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,82</t>
+          <t>0,0; 59,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,67</t>
+          <t>0,0; 22,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,89</t>
+          <t>0,0; 26,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 24,87</t>
+          <t>2,28; 23,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,67</t>
+          <t>0,0; 11,8</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,54</t>
+          <t>1,47; 12,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,21</t>
+          <t>1,07; 9,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>0,0; 7,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,79</t>
+          <t>0,0; 10,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,56</t>
+          <t>0,0; 5,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>0,0; 5,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,21</t>
+          <t>1,49; 9,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,97</t>
+          <t>0,54; 5,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>0,0; 4,09</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor abdominal (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2565</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2685</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3866</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3321</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3374</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2912</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3379</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3026</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3750</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2956</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3276</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3361</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3353</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4097</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1782</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3470</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3110</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3703</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>449; 4538</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2814</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2730</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>644; 5487</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>658; 5885</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3876</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4733</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3279</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0; 2663</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1345; 8154</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>679; 6931</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4210</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$abdomen-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$abdomen-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor abdominal (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor abdominal (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,89</t>
+          <t>0,0; 24,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,13</t>
+          <t>0,0; 45,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,97</t>
+          <t>0,0; 23,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,3</t>
+          <t>0,0; 32,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,28</t>
+          <t>0,0; 18,14</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,7</t>
+          <t>0,0; 33,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,9</t>
+          <t>0,0; 22,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,95</t>
+          <t>0,0; 57,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,56</t>
+          <t>0,0; 31,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,04</t>
+          <t>0,0; 36,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,76</t>
+          <t>0,0; 39,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,65</t>
+          <t>0,0; 48,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,87</t>
+          <t>0,0; 30,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,04</t>
+          <t>0,0; 30,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,8</t>
+          <t>0,0; 59,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,93</t>
+          <t>0,0; 22,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,66</t>
+          <t>0,0; 29,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,28; 23,04</t>
+          <t>2,26; 22,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,8</t>
+          <t>0,0; 14,71</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,51</t>
+          <t>1,42; 12,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,6</t>
+          <t>1,07; 9,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,03</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>0,0; 8,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,16</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,56</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 9,0</t>
+          <t>1,46; 8,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,55</t>
+          <t>0,55; 5,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 4,55</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor abdominal (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor abdominal (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2565</t>
+          <t>0; 2566</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2685</t>
+          <t>0; 2658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3866</t>
+          <t>0; 3834</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3321</t>
+          <t>0; 3098</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3374</t>
+          <t>0; 3541</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2912</t>
+          <t>0; 2825</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3379</t>
+          <t>0; 3328</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3026</t>
+          <t>0; 3025</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3750</t>
+          <t>0; 3210</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2956</t>
+          <t>0; 2727</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 3276</t>
+          <t>0; 2855</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3361</t>
+          <t>0; 2944</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3353</t>
+          <t>0; 3541</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 4097</t>
+          <t>0; 4016</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3470</t>
+          <t>0; 3468</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3110</t>
+          <t>0; 3040</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3703</t>
+          <t>0; 4119</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>449; 4538</t>
+          <t>446; 4443</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 2814</t>
+          <t>0; 3507</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>644; 5487</t>
+          <t>624; 5439</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>658; 5885</t>
+          <t>653; 6056</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 3876</t>
+          <t>0; 3371</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0; 4733</t>
+          <t>0; 4032</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 3279</t>
+          <t>0; 3789</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 2663</t>
+          <t>0; 3267</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1345; 8154</t>
+          <t>1320; 7573</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>679; 6931</t>
+          <t>690; 6467</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0; 4210</t>
+          <t>0; 4688</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$abdomen-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$abdomen-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -735,22 +735,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,03%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,94%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,9</t>
+          <t>0,0; 48,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,66</t>
+          <t>0,0; 29,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,77</t>
+          <t>0,0; 26,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 28,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,14</t>
+          <t>0,0; 17,04</t>
         </is>
       </c>
     </row>
@@ -1070,22 +1070,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,85%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 35,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,55</t>
+          <t>0,0; 22,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>14,3%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 44,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,3</t>
+          <t>0,0; 35,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,27 +1285,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,79%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>9,48%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,89</t>
+          <t>0,0; 45,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 35,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,75</t>
+          <t>0,0; 42,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,49</t>
+          <t>0,0; 29,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,43</t>
+          <t>0,0; 31,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>18,64%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>5,07%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,76</t>
+          <t>0,0; 26,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,65</t>
+          <t>0,0; 51,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 25,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 22,56</t>
+          <t>2,24; 24,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,71</t>
+          <t>0,0; 15,67</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>5,38%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>3,4%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1,25%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,39</t>
+          <t>0,0; 8,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,88</t>
+          <t>0,0; 4,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,6</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1,44; 12,54</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,07; 9,21</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>0,0; 6,12</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,63</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,96</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,83</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,36</t>
+          <t>1,72; 8,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,18</t>
+          <t>0,58; 4,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,55</t>
+          <t>0,0; 4,19</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1971,22 +1971,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>613</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2566</t>
+          <t>0; 2804</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2658</t>
+          <t>0; 2999</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3834</t>
+          <t>0; 4205</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2806</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3098</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3541</t>
+          <t>0; 3327</t>
         </is>
       </c>
     </row>
@@ -2412,22 +2412,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2465,22 +2465,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>659</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2825</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2981</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3328</t>
+          <t>0; 3375</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2575,22 +2575,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2628,22 +2628,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>747</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3025</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2315</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3210</t>
+          <t>0; 3688</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2733,22 +2733,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2786,27 +2786,27 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>665</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>678</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2727</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2855</t>
+          <t>0; 2765</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2717</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2944</t>
+          <t>0; 3025</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3541</t>
+          <t>0; 3407</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 4016</t>
+          <t>0; 4106</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>1082</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>687</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3468</t>
+          <t>0; 3736</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3040</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4119</t>
+          <t>0; 3007</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3481</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>446; 4443</t>
+          <t>442; 4899</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3507</t>
+          <t>0; 3736</t>
         </is>
       </c>
     </row>
@@ -3059,27 +3059,27 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>2360</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>2084</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>687</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>624; 5439</t>
+          <t>0; 4107</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>653; 6056</t>
+          <t>0; 2901</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 3371</t>
+          <t>0; 3157</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0; 4032</t>
+          <t>631; 5504</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 3789</t>
+          <t>653; 5642</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 3267</t>
+          <t>0; 3372</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1320; 7573</t>
+          <t>1555; 7439</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>690; 6467</t>
+          <t>724; 6199</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0; 4688</t>
+          <t>0; 4316</t>
         </is>
       </c>
     </row>
